--- a/FEHSimulation/Spreadsheets/FEHSpecials.xlsx
+++ b/FEHSimulation/Spreadsheets/FEHSpecials.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="546">
   <si>
     <t>Name</t>
   </si>
@@ -1656,6 +1656,29 @@
   </si>
   <si>
     <t>trueNjorun</t>
+  </si>
+  <si>
+    <t>Archrival</t>
+  </si>
+  <si>
+    <t>archrival</t>
+  </si>
+  <si>
+    <t>Celestial Form</t>
+  </si>
+  <si>
+    <t>Boosts damage by X% of unit's Spd when Special triggers (if any space within 2 spaces of unit or foe has a Divine Vein effect applied, is defensive terrain, or counts as difficult or impassable terrain for units other than flying, X = 60; otherwise, X = 40).
+If unit's or foe's Special is ready, or unit's or foe's Special triggered before or during this combat, and also, if unit's Spd ≥ foe's Spd-4 or any space within 2 spaces of unit or foe has a Divine Vein effect applied, is defensive terrain, or counts as difficult or impassable terrain for units other than flying, reduces damage from foe's next attack by 40% (once per combat; excluding area-of-effect Specials).</t>
+  </si>
+  <si>
+    <t>celestialSpdSp</t>
+  </si>
+  <si>
+    <t>Inf-Armor-Cav</t>
+  </si>
+  <si>
+    <t>When Special triggers, boosts damage by X% of the greater of unit's or foe's Atk (if unit has weapon-triangle advantage, X = 80; otherwise, X = 70).
+Reduces damage from foe's first attack by 40% ("first attack" normally means only the first strike; for effects that grant "unit attacks twice," it means the first and second strikes) and inflicts Special cooldown charge -1 on foe per attack during combat (only highest value applied; does not stack), and also, if unit has weapon-triangle advantage, grants Special cooldown count-2 to unit and inflicts Special cooldown count+2 on foe before unit's first attack during combat (cannot exceed foe's maximum Special cooldown).</t>
   </si>
 </sst>
 </file>
@@ -1974,7 +1997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q164"/>
+  <dimension ref="A1:Q166"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3491,10 +3514,10 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>128</v>
+        <v>541</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>129</v>
+        <v>542</v>
       </c>
       <c r="C41" s="1">
         <v>3</v>
@@ -3503,10 +3526,10 @@
         <v>19</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>130</v>
+        <v>543</v>
       </c>
       <c r="F41" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -3515,10 +3538,10 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>21</v>
+        <v>544</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>22</v>
+        <v>163</v>
       </c>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
@@ -3526,22 +3549,22 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>131</v>
+        <v>539</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>129</v>
+        <v>545</v>
       </c>
       <c r="C42" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="F42" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -3553,7 +3576,7 @@
         <v>21</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -3561,10 +3584,10 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C43" s="1">
         <v>3</v>
@@ -3576,7 +3599,7 @@
         <v>130</v>
       </c>
       <c r="F43" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -3596,22 +3619,22 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C44" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F44" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -3631,22 +3654,22 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C45" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F45" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -3666,10 +3689,10 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C46" s="1">
         <v>3</v>
@@ -3681,7 +3704,7 @@
         <v>136</v>
       </c>
       <c r="F46" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -3701,13 +3724,13 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C47" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>19</v>
@@ -3716,14 +3739,10 @@
         <v>136</v>
       </c>
       <c r="F47" s="1">
-        <v>5</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H47" s="1">
-        <v>50</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3740,29 +3759,25 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C48" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F48" s="1">
-        <v>1</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H48" s="1">
-        <v>1</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -3779,28 +3794,28 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C49" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F49" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="H49" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -3818,7 +3833,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>143</v>
@@ -3833,7 +3848,7 @@
         <v>145</v>
       </c>
       <c r="F50" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>146</v>
@@ -3857,7 +3872,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>143</v>
@@ -3872,13 +3887,13 @@
         <v>145</v>
       </c>
       <c r="F51" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>146</v>
       </c>
       <c r="H51" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -3896,10 +3911,10 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C52" s="1">
         <v>4</v>
@@ -3911,13 +3926,13 @@
         <v>145</v>
       </c>
       <c r="F52" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>146</v>
       </c>
       <c r="H52" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -3935,10 +3950,10 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
@@ -3950,7 +3965,7 @@
         <v>145</v>
       </c>
       <c r="F53" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>146</v>
@@ -3974,7 +3989,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>151</v>
@@ -3989,13 +4004,13 @@
         <v>145</v>
       </c>
       <c r="F54" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>146</v>
       </c>
       <c r="H54" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -4013,7 +4028,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>151</v>
@@ -4028,13 +4043,13 @@
         <v>145</v>
       </c>
       <c r="F55" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>146</v>
       </c>
       <c r="H55" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -4052,10 +4067,10 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C56" s="1">
         <v>4</v>
@@ -4067,7 +4082,7 @@
         <v>145</v>
       </c>
       <c r="F56" s="1">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>146</v>
@@ -4091,10 +4106,10 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C57" s="1">
         <v>4</v>
@@ -4106,13 +4121,13 @@
         <v>145</v>
       </c>
       <c r="F57" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>146</v>
       </c>
       <c r="H57" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -4130,7 +4145,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>143</v>
@@ -4145,13 +4160,13 @@
         <v>145</v>
       </c>
       <c r="F58" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>146</v>
       </c>
       <c r="H58" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -4169,7 +4184,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>143</v>
@@ -4184,7 +4199,7 @@
         <v>145</v>
       </c>
       <c r="F59" s="1">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>146</v>
@@ -4208,25 +4223,29 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="C60" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="F60" s="1">
-        <v>3</v>
-      </c>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H60" s="1">
+        <v>2</v>
+      </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -4235,7 +4254,7 @@
         <v>21</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>163</v>
+        <v>22</v>
       </c>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
@@ -4243,25 +4262,29 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="C61" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="F61" s="1">
-        <v>3</v>
-      </c>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H61" s="1">
+        <v>1</v>
+      </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -4270,7 +4293,7 @@
         <v>21</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>163</v>
+        <v>22</v>
       </c>
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
@@ -4278,10 +4301,10 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C62" s="1">
         <v>3</v>
@@ -4293,7 +4316,7 @@
         <v>162</v>
       </c>
       <c r="F62" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -4313,19 +4336,19 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C63" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>161</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F63" s="1">
         <v>3</v>
@@ -4348,22 +4371,22 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C64" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>161</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F64" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -4383,10 +4406,10 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C65" s="1">
         <v>3</v>
@@ -4398,7 +4421,7 @@
         <v>169</v>
       </c>
       <c r="F65" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -4418,22 +4441,22 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C66" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>161</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F66" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -4442,10 +4465,10 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
@@ -4453,22 +4476,22 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C67" s="1">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F67" s="1">
         <v>5</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F67" s="1">
-        <v>0</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -4480,7 +4503,7 @@
         <v>21</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
@@ -4488,19 +4511,19 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C68" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -4512,10 +4535,10 @@
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="O68" s="1"/>
       <c r="P68" s="1"/>
@@ -4523,22 +4546,22 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C69" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F69" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -4550,7 +4573,7 @@
         <v>21</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
@@ -4558,22 +4581,22 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C70" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F70" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -4585,7 +4608,7 @@
         <v>21</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="O70" s="1"/>
       <c r="P70" s="1"/>
@@ -4593,10 +4616,10 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C71" s="1">
         <v>1</v>
@@ -4605,10 +4628,10 @@
         <v>186</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F71" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -4628,22 +4651,22 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C72" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>186</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F72" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -4663,10 +4686,10 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C73" s="1">
         <v>1</v>
@@ -4675,7 +4698,7 @@
         <v>186</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="F73" s="1">
         <v>4</v>
@@ -4698,10 +4721,10 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C74" s="1">
         <v>1</v>
@@ -4710,7 +4733,7 @@
         <v>186</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F74" s="1">
         <v>4</v>
@@ -4733,10 +4756,10 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
@@ -4745,17 +4768,13 @@
         <v>186</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F75" s="1">
         <v>4</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="H75" s="1">
-        <v>4</v>
-      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
@@ -4772,10 +4791,10 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C76" s="1">
         <v>1</v>
@@ -4784,17 +4803,13 @@
         <v>186</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F76" s="1">
-        <v>6</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="H76" s="1">
-        <v>6</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
@@ -4811,10 +4826,10 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
@@ -4829,7 +4844,7 @@
         <v>4</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H77" s="1">
         <v>4</v>
@@ -4850,10 +4865,10 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C78" s="1">
         <v>1</v>
@@ -4868,7 +4883,7 @@
         <v>6</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H78" s="1">
         <v>6</v>
@@ -4889,10 +4904,10 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C79" s="1">
         <v>1</v>
@@ -4907,7 +4922,7 @@
         <v>4</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H79" s="1">
         <v>4</v>
@@ -4928,10 +4943,10 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C80" s="1">
         <v>1</v>
@@ -4946,7 +4961,7 @@
         <v>6</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H80" s="1">
         <v>6</v>
@@ -4967,10 +4982,10 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C81" s="1">
         <v>1</v>
@@ -4979,13 +4994,13 @@
         <v>186</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F81" s="1">
         <v>4</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H81" s="1">
         <v>4</v>
@@ -5006,10 +5021,10 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C82" s="1">
         <v>1</v>
@@ -5018,13 +5033,13 @@
         <v>186</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F82" s="1">
         <v>6</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H82" s="1">
         <v>6</v>
@@ -5045,10 +5060,10 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C83" s="1">
         <v>1</v>
@@ -5063,7 +5078,7 @@
         <v>4</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H83" s="1">
         <v>4</v>
@@ -5084,10 +5099,10 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C84" s="1">
         <v>1</v>
@@ -5102,7 +5117,7 @@
         <v>6</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H84" s="1">
         <v>6</v>
@@ -5123,10 +5138,10 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C85" s="1">
         <v>1</v>
@@ -5135,7 +5150,7 @@
         <v>186</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F85" s="1">
         <v>4</v>
@@ -5162,10 +5177,10 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C86" s="1">
         <v>1</v>
@@ -5174,7 +5189,7 @@
         <v>186</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F86" s="1">
         <v>6</v>
@@ -5201,28 +5216,28 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C87" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="F87" s="1">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="H87" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -5240,28 +5255,28 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C88" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="F88" s="1">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="H88" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -5279,13 +5294,13 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C89" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>19</v>
@@ -5294,10 +5309,10 @@
         <v>230</v>
       </c>
       <c r="F89" s="1">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -5318,13 +5333,13 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C90" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>19</v>
@@ -5333,10 +5348,10 @@
         <v>230</v>
       </c>
       <c r="F90" s="1">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -5357,25 +5372,29 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C91" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="F91" s="1">
-        <v>80</v>
-      </c>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
@@ -5384,24 +5403,18 @@
         <v>21</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O91" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="P91" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q91" s="1" t="s">
-        <v>245</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="1"/>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C92" s="1">
         <v>3</v>
@@ -5410,13 +5423,13 @@
         <v>19</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="F92" s="1">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -5429,32 +5442,30 @@
         <v>21</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O92" s="1" t="s">
-        <v>249</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="C93" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="F93" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -5469,36 +5480,36 @@
         <v>22</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="Q93" s="1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C94" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="F94" s="1">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
@@ -5514,38 +5525,32 @@
         <v>22</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="P94" s="1" t="s">
-        <v>259</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="P94" s="1"/>
       <c r="Q94" s="1"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C95" s="1">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>169</v>
+        <v>119</v>
       </c>
       <c r="F95" s="1">
-        <v>4</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="H95" s="1">
-        <v>0</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
@@ -5557,35 +5562,39 @@
         <v>22</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="P95" s="1"/>
-      <c r="Q95" s="1"/>
+        <v>252</v>
+      </c>
+      <c r="P95" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q95" s="1" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C96" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="F96" s="1">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="H96" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
@@ -5598,46 +5607,40 @@
         <v>22</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q96" s="1" t="s">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Q96" s="1"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C97" s="1">
+        <v>2</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F97" s="1">
         <v>4</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F97" s="1">
-        <v>50</v>
-      </c>
       <c r="G97" s="1" t="s">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="H97" s="1">
-        <v>50</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="J97" s="1">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="1" t="s">
@@ -5647,35 +5650,35 @@
         <v>22</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C98" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="F98" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="H98" s="1">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
@@ -5688,43 +5691,45 @@
         <v>22</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q98" s="1"/>
+        <v>266</v>
+      </c>
+      <c r="Q98" s="1" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C99" s="1">
+        <v>4</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F99" s="1">
+        <v>50</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H99" s="1">
+        <v>50</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J99" s="1">
         <v>2</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F99" s="1">
-        <v>35</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="H99" s="1">
-        <v>6</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="J99" s="1">
-        <v>6</v>
       </c>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
@@ -5735,19 +5740,17 @@
         <v>22</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="P99" s="1" t="s">
-        <v>277</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C100" s="1">
         <v>2</v>
@@ -5759,13 +5762,13 @@
         <v>119</v>
       </c>
       <c r="F100" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>77</v>
+        <v>271</v>
       </c>
       <c r="H100" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -5778,19 +5781,19 @@
         <v>22</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="P100" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="Q100" s="1"/>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C101" s="1">
         <v>2</v>
@@ -5802,19 +5805,19 @@
         <v>119</v>
       </c>
       <c r="F101" s="1">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>77</v>
+        <v>271</v>
       </c>
       <c r="H101" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>50</v>
+        <v>275</v>
       </c>
       <c r="J101" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -5825,17 +5828,19 @@
         <v>22</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="P101" s="1"/>
+        <v>273</v>
+      </c>
+      <c r="P101" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="Q101" s="1"/>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C102" s="1">
         <v>2</v>
@@ -5847,13 +5852,13 @@
         <v>119</v>
       </c>
       <c r="F102" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="H102" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -5866,21 +5871,19 @@
         <v>22</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q102" s="1" t="s">
-        <v>288</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="Q102" s="1"/>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C103" s="1">
         <v>2</v>
@@ -5892,16 +5895,16 @@
         <v>119</v>
       </c>
       <c r="F103" s="1">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="H103" s="1">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>291</v>
+        <v>50</v>
       </c>
       <c r="J103" s="1">
         <v>0</v>
@@ -5915,35 +5918,35 @@
         <v>22</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C104" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="F104" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>294</v>
+        <v>136</v>
       </c>
       <c r="H104" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -5956,43 +5959,45 @@
         <v>22</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="P104" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q104" s="1"/>
+        <v>287</v>
+      </c>
+      <c r="Q104" s="1" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C105" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="F105" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>294</v>
+        <v>136</v>
       </c>
       <c r="H105" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="J105" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -6003,32 +6008,32 @@
         <v>22</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C106" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="F106" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>50</v>
+        <v>294</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -6044,40 +6049,44 @@
         <v>22</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="P106" s="1" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="Q106" s="1"/>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C107" s="1">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="F107" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>136</v>
+        <v>294</v>
       </c>
       <c r="H107" s="1">
-        <v>25</v>
-      </c>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J107" s="1">
+        <v>1</v>
+      </c>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
       <c r="M107" s="1" t="s">
@@ -6087,21 +6096,17 @@
         <v>22</v>
       </c>
       <c r="O107" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="P107" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q107" s="1" t="s">
-        <v>307</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="P107" s="1"/>
+      <c r="Q107" s="1"/>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>251</v>
+        <v>300</v>
       </c>
       <c r="C108" s="1">
         <v>2</v>
@@ -6110,13 +6115,17 @@
         <v>19</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="F108" s="1">
-        <v>40</v>
-      </c>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H108" s="1">
+        <v>0</v>
+      </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
@@ -6128,35 +6137,37 @@
         <v>22</v>
       </c>
       <c r="O108" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="P108" s="1"/>
+        <v>301</v>
+      </c>
+      <c r="P108" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="Q108" s="1"/>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="C109" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="F109" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>271</v>
+        <v>136</v>
       </c>
       <c r="H109" s="1">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -6169,17 +6180,21 @@
         <v>22</v>
       </c>
       <c r="O109" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="P109" s="1"/>
-      <c r="Q109" s="1"/>
+        <v>305</v>
+      </c>
+      <c r="P109" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q109" s="1" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>313</v>
+        <v>251</v>
       </c>
       <c r="C110" s="1">
         <v>2</v>
@@ -6191,14 +6206,10 @@
         <v>119</v>
       </c>
       <c r="F110" s="1">
-        <v>30</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="H110" s="1">
-        <v>10</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
@@ -6210,35 +6221,35 @@
         <v>22</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="P110" s="1"/>
       <c r="Q110" s="1"/>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C111" s="1">
+        <v>2</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F111" s="1">
+        <v>30</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H111" s="1">
         <v>4</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F111" s="1">
-        <v>50</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H111" s="1">
-        <v>50</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -6251,35 +6262,35 @@
         <v>22</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="P111" s="1"/>
       <c r="Q111" s="1"/>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C112" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>320</v>
+        <v>119</v>
       </c>
       <c r="F112" s="1">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="H112" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -6292,44 +6303,38 @@
         <v>22</v>
       </c>
       <c r="O112" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="P112" s="1" t="s">
-        <v>323</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="P112" s="1"/>
       <c r="Q112" s="1"/>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>325</v>
+        <v>264</v>
       </c>
       <c r="C113" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>320</v>
+        <v>136</v>
       </c>
       <c r="F113" s="1">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>321</v>
+        <v>77</v>
       </c>
       <c r="H113" s="1">
-        <v>40</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="J113" s="1">
-        <v>2</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
       <c r="M113" s="1" t="s">
@@ -6339,42 +6344,38 @@
         <v>22</v>
       </c>
       <c r="O113" s="1" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="P113" s="1"/>
       <c r="Q113" s="1"/>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="C114" s="1">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="F114" s="1">
         <v>3</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="H114" s="1">
-        <v>0</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="J114" s="1">
-        <v>0</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
       <c r="M114" s="1" t="s">
@@ -6384,43 +6385,43 @@
         <v>22</v>
       </c>
       <c r="O114" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="Q114" s="1"/>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C115" s="1">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="F115" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="H115" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="J115" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
@@ -6431,38 +6432,42 @@
         <v>22</v>
       </c>
       <c r="O115" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C116" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>145</v>
+        <v>270</v>
       </c>
       <c r="F116" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>146</v>
+        <v>330</v>
       </c>
       <c r="H116" s="1">
         <v>0</v>
       </c>
-      <c r="I116" s="1"/>
-      <c r="J116" s="1"/>
+      <c r="I116" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="J116" s="1">
+        <v>0</v>
+      </c>
       <c r="K116" s="1"/>
       <c r="L116" s="1"/>
       <c r="M116" s="1" t="s">
@@ -6472,40 +6477,40 @@
         <v>22</v>
       </c>
       <c r="O116" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="P116" s="1" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="Q116" s="1"/>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C117" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>145</v>
+        <v>336</v>
       </c>
       <c r="F117" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>146</v>
+        <v>330</v>
       </c>
       <c r="H117" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="J117" s="1">
         <v>0</v>
@@ -6519,32 +6524,32 @@
         <v>22</v>
       </c>
       <c r="O117" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C118" s="1">
         <v>2</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>19</v>
+        <v>144</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="F118" s="1">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>347</v>
+        <v>146</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -6560,38 +6565,44 @@
         <v>22</v>
       </c>
       <c r="O118" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="P118" s="1"/>
+        <v>340</v>
+      </c>
+      <c r="P118" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="Q118" s="1"/>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C119" s="1">
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>19</v>
+        <v>144</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="F119" s="1">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>351</v>
+        <v>146</v>
       </c>
       <c r="H119" s="1">
-        <v>0</v>
-      </c>
-      <c r="I119" s="1"/>
-      <c r="J119" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="J119" s="1">
+        <v>0</v>
+      </c>
       <c r="K119" s="1"/>
       <c r="L119" s="1"/>
       <c r="M119" s="1" t="s">
@@ -6601,17 +6612,17 @@
         <v>22</v>
       </c>
       <c r="O119" s="1" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="P119" s="1"/>
       <c r="Q119" s="1"/>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C120" s="1">
         <v>2</v>
@@ -6620,13 +6631,13 @@
         <v>19</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>354</v>
+        <v>91</v>
       </c>
       <c r="F120" s="1">
         <v>25</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>50</v>
+        <v>347</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
@@ -6642,19 +6653,17 @@
         <v>22</v>
       </c>
       <c r="O120" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="P120" s="1" t="s">
-        <v>356</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="P120" s="1"/>
       <c r="Q120" s="1"/>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C121" s="1">
         <v>2</v>
@@ -6663,23 +6672,19 @@
         <v>19</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>354</v>
+        <v>91</v>
       </c>
       <c r="F121" s="1">
         <v>30</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>50</v>
+        <v>351</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
       </c>
-      <c r="I121" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="J121" s="1">
-        <v>3</v>
-      </c>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
       <c r="M121" s="1" t="s">
@@ -6689,32 +6694,36 @@
         <v>22</v>
       </c>
       <c r="O121" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="P121" s="1"/>
       <c r="Q121" s="1"/>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C122" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="F122" s="1">
-        <v>0</v>
-      </c>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H122" s="1">
+        <v>0</v>
+      </c>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
       <c r="K122" s="1"/>
@@ -6726,41 +6735,43 @@
         <v>22</v>
       </c>
       <c r="O122" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="P122" s="1"/>
+        <v>355</v>
+      </c>
+      <c r="P122" s="1" t="s">
+        <v>356</v>
+      </c>
       <c r="Q122" s="1"/>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C123" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>182</v>
+        <v>19</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>183</v>
+        <v>354</v>
       </c>
       <c r="F123" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>366</v>
+        <v>50</v>
       </c>
       <c r="H123" s="1">
         <v>0</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>270</v>
+        <v>359</v>
       </c>
       <c r="J123" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K123" s="1"/>
       <c r="L123" s="1"/>
@@ -6771,42 +6782,34 @@
         <v>22</v>
       </c>
       <c r="O123" s="1" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C124" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>183</v>
+        <v>362</v>
       </c>
       <c r="F124" s="1">
         <v>0</v>
       </c>
-      <c r="G124" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="H124" s="1">
-        <v>0</v>
-      </c>
-      <c r="I124" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="J124" s="1">
-        <v>5</v>
-      </c>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
       <c r="M124" s="1" t="s">
@@ -6816,38 +6819,42 @@
         <v>22</v>
       </c>
       <c r="O124" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="P124" s="1"/>
       <c r="Q124" s="1"/>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>365</v>
       </c>
       <c r="C125" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>19</v>
+        <v>182</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="F125" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G125" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H125" s="1">
+        <v>0</v>
+      </c>
+      <c r="I125" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H125" s="1">
-        <v>3</v>
-      </c>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
+      <c r="J125" s="1">
+        <v>5</v>
+      </c>
       <c r="K125" s="1"/>
       <c r="L125" s="1"/>
       <c r="M125" s="1" t="s">
@@ -6857,38 +6864,42 @@
         <v>22</v>
       </c>
       <c r="O125" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C126" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>19</v>
+        <v>182</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>375</v>
+        <v>183</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="H126" s="1">
-        <v>3</v>
-      </c>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J126" s="1">
+        <v>5</v>
+      </c>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
       <c r="M126" s="1" t="s">
@@ -6898,35 +6909,35 @@
         <v>22</v>
       </c>
       <c r="O126" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="P126" s="1"/>
       <c r="Q126" s="1"/>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="C127" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="F127" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>378</v>
+        <v>270</v>
       </c>
       <c r="H127" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
@@ -6939,37 +6950,35 @@
         <v>22</v>
       </c>
       <c r="O127" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="P127" s="1" t="s">
-        <v>380</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="P127" s="1"/>
       <c r="Q127" s="1"/>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C128" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>35</v>
+        <v>375</v>
       </c>
       <c r="F128" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>383</v>
+        <v>336</v>
       </c>
       <c r="H128" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
@@ -6982,17 +6991,17 @@
         <v>22</v>
       </c>
       <c r="O128" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="P128" s="1"/>
       <c r="Q128" s="1"/>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C129" s="1">
         <v>2</v>
@@ -7001,29 +7010,21 @@
         <v>19</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="F129" s="1">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>50</v>
+        <v>378</v>
       </c>
       <c r="H129" s="1">
         <v>0</v>
       </c>
-      <c r="I129" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="J129" s="1">
-        <v>0</v>
-      </c>
-      <c r="K129" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="L129" s="1">
-        <v>0</v>
-      </c>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
       <c r="M129" s="1" t="s">
         <v>21</v>
       </c>
@@ -7031,17 +7032,19 @@
         <v>22</v>
       </c>
       <c r="O129" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="P129" s="1"/>
+        <v>379</v>
+      </c>
+      <c r="P129" s="1" t="s">
+        <v>380</v>
+      </c>
       <c r="Q129" s="1"/>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C130" s="1">
         <v>2</v>
@@ -7050,23 +7053,19 @@
         <v>19</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="F130" s="1">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>50</v>
+        <v>383</v>
       </c>
       <c r="H130" s="1">
         <v>0</v>
       </c>
-      <c r="I130" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="J130" s="1">
-        <v>0</v>
-      </c>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
       <c r="K130" s="1"/>
       <c r="L130" s="1"/>
       <c r="M130" s="1" t="s">
@@ -7076,36 +7075,48 @@
         <v>22</v>
       </c>
       <c r="O130" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="P130" s="1"/>
       <c r="Q130" s="1"/>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C131" s="1">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>393</v>
+        <v>35</v>
       </c>
       <c r="F131" s="1">
-        <v>0</v>
-      </c>
-      <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
-      <c r="K131" s="1"/>
-      <c r="L131" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H131" s="1">
+        <v>0</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J131" s="1">
+        <v>0</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L131" s="1">
+        <v>0</v>
+      </c>
       <c r="M131" s="1" t="s">
         <v>21</v>
       </c>
@@ -7113,17 +7124,17 @@
         <v>22</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="P131" s="1"/>
       <c r="Q131" s="1"/>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -7138,13 +7149,13 @@
         <v>25</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>359</v>
+        <v>50</v>
       </c>
       <c r="H132" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>397</v>
+        <v>291</v>
       </c>
       <c r="J132" s="1">
         <v>0</v>
@@ -7158,42 +7169,34 @@
         <v>22</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="P132" s="1"/>
       <c r="Q132" s="1"/>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C133" s="1">
         <v>2</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>119</v>
+        <v>393</v>
       </c>
       <c r="F133" s="1">
-        <v>40</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="H133" s="1">
-        <v>3</v>
-      </c>
-      <c r="I133" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="J133" s="1">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
       <c r="K133" s="1"/>
       <c r="L133" s="1"/>
       <c r="M133" s="1" t="s">
@@ -7203,38 +7206,42 @@
         <v>22</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="P133" s="1"/>
       <c r="Q133" s="1"/>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C134" s="1">
+        <v>2</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F134" s="1">
+        <v>25</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="H134" s="1">
         <v>3</v>
       </c>
-      <c r="D134" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F134" s="1">
-        <v>50</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H134" s="1">
-        <v>0</v>
-      </c>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1"/>
+      <c r="I134" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="J134" s="1">
+        <v>0</v>
+      </c>
       <c r="K134" s="1"/>
       <c r="L134" s="1"/>
       <c r="M134" s="1" t="s">
@@ -7244,38 +7251,38 @@
         <v>22</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="P134" s="1"/>
       <c r="Q134" s="1"/>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C135" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>409</v>
+        <v>119</v>
       </c>
       <c r="F135" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>291</v>
+        <v>359</v>
       </c>
       <c r="H135" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="J135" s="1">
         <v>0</v>
@@ -7289,19 +7296,17 @@
         <v>22</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="P135" s="1" t="s">
-        <v>412</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="P135" s="1"/>
       <c r="Q135" s="1"/>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C136" s="1">
         <v>3</v>
@@ -7313,20 +7318,16 @@
         <v>119</v>
       </c>
       <c r="F136" s="1">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>291</v>
+        <v>405</v>
       </c>
       <c r="H136" s="1">
         <v>0</v>
       </c>
-      <c r="I136" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="J136" s="1">
-        <v>0</v>
-      </c>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
       <c r="K136" s="1"/>
       <c r="L136" s="1"/>
       <c r="M136" s="1" t="s">
@@ -7336,41 +7337,41 @@
         <v>22</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="1"/>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C137" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="F137" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>50</v>
+        <v>291</v>
       </c>
       <c r="H137" s="1">
         <v>0</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>354</v>
+        <v>410</v>
       </c>
       <c r="J137" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K137" s="1"/>
       <c r="L137" s="1"/>
@@ -7381,29 +7382,31 @@
         <v>22</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="P137" s="1"/>
+        <v>411</v>
+      </c>
+      <c r="P137" s="1" t="s">
+        <v>412</v>
+      </c>
       <c r="Q137" s="1"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C138" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="F138" s="1">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>291</v>
@@ -7412,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="J138" s="1">
         <v>0</v>
@@ -7426,17 +7429,17 @@
         <v>22</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="P138" s="1"/>
       <c r="Q138" s="1"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C139" s="1">
         <v>2</v>
@@ -7445,29 +7448,25 @@
         <v>19</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>119</v>
+        <v>419</v>
       </c>
       <c r="F139" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>248</v>
+        <v>50</v>
       </c>
       <c r="H139" s="1">
         <v>0</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>291</v>
+        <v>354</v>
       </c>
       <c r="J139" s="1">
-        <v>0</v>
-      </c>
-      <c r="K139" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="L139" s="1">
-        <v>100</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="K139" s="1"/>
+      <c r="L139" s="1"/>
       <c r="M139" s="1" t="s">
         <v>21</v>
       </c>
@@ -7475,38 +7474,42 @@
         <v>22</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="P139" s="1"/>
       <c r="Q139" s="1"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C140" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>431</v>
+        <v>35</v>
       </c>
       <c r="F140" s="1">
         <v>40</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>432</v>
+        <v>291</v>
       </c>
       <c r="H140" s="1">
-        <v>17</v>
-      </c>
-      <c r="I140" s="1"/>
-      <c r="J140" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="J140" s="1">
+        <v>0</v>
+      </c>
       <c r="K140" s="1"/>
       <c r="L140" s="1"/>
       <c r="M140" s="1" t="s">
@@ -7516,17 +7519,17 @@
         <v>22</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="P140" s="1"/>
       <c r="Q140" s="1"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="C141" s="1">
         <v>2</v>
@@ -7541,22 +7544,22 @@
         <v>40</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>50</v>
+        <v>248</v>
       </c>
       <c r="H141" s="1">
         <v>0</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="J141" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="L141" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>21</v>
@@ -7565,35 +7568,35 @@
         <v>22</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="P141" s="1"/>
       <c r="Q141" s="1"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C142" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>35</v>
+        <v>431</v>
       </c>
       <c r="F142" s="1">
         <v>40</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="H142" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -7606,17 +7609,17 @@
         <v>22</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="1"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C143" s="1">
         <v>2</v>
@@ -7625,7 +7628,7 @@
         <v>19</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="F143" s="1">
         <v>40</v>
@@ -7637,13 +7640,17 @@
         <v>0</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>444</v>
+        <v>314</v>
       </c>
       <c r="J143" s="1">
-        <v>0</v>
-      </c>
-      <c r="K143" s="1"/>
-      <c r="L143" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="L143" s="1">
+        <v>0</v>
+      </c>
       <c r="M143" s="1" t="s">
         <v>21</v>
       </c>
@@ -7651,17 +7658,17 @@
         <v>22</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C144" s="1">
         <v>2</v>
@@ -7670,23 +7677,19 @@
         <v>19</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="F144" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>291</v>
+        <v>440</v>
       </c>
       <c r="H144" s="1">
         <v>0</v>
       </c>
-      <c r="I144" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="J144" s="1">
-        <v>0</v>
-      </c>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1"/>
       <c r="K144" s="1"/>
       <c r="L144" s="1"/>
       <c r="M144" s="1" t="s">
@@ -7696,17 +7699,17 @@
         <v>22</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="P144" s="1"/>
       <c r="Q144" s="1"/>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C145" s="1">
         <v>2</v>
@@ -7715,29 +7718,25 @@
         <v>19</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F145" s="1">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>451</v>
+        <v>50</v>
       </c>
       <c r="H145" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>359</v>
+        <v>444</v>
       </c>
       <c r="J145" s="1">
-        <v>3</v>
-      </c>
-      <c r="K145" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="L145" s="1">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K145" s="1"/>
+      <c r="L145" s="1"/>
       <c r="M145" s="1" t="s">
         <v>21</v>
       </c>
@@ -7745,20 +7744,20 @@
         <v>22</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="P145" s="1"/>
       <c r="Q145" s="1"/>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C146" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>19</v>
@@ -7767,16 +7766,20 @@
         <v>119</v>
       </c>
       <c r="F146" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>456</v>
+        <v>291</v>
       </c>
       <c r="H146" s="1">
-        <v>3</v>
-      </c>
-      <c r="I146" s="1"/>
-      <c r="J146" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="J146" s="1">
+        <v>0</v>
+      </c>
       <c r="K146" s="1"/>
       <c r="L146" s="1"/>
       <c r="M146" s="1" t="s">
@@ -7786,17 +7789,17 @@
         <v>22</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="P146" s="1"/>
       <c r="Q146" s="1"/>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C147" s="1">
         <v>2</v>
@@ -7805,21 +7808,29 @@
         <v>19</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>460</v>
+        <v>91</v>
       </c>
       <c r="F147" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="H147" s="1">
-        <v>0</v>
-      </c>
-      <c r="I147" s="1"/>
-      <c r="J147" s="1"/>
-      <c r="K147" s="1"/>
-      <c r="L147" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J147" s="1">
+        <v>3</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="L147" s="1">
+        <v>0</v>
+      </c>
       <c r="M147" s="1" t="s">
         <v>21</v>
       </c>
@@ -7827,42 +7838,38 @@
         <v>22</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="P147" s="1"/>
       <c r="Q147" s="1"/>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="C148" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>169</v>
+        <v>119</v>
       </c>
       <c r="F148" s="1">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="H148" s="1">
-        <v>0</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="J148" s="1">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I148" s="1"/>
+      <c r="J148" s="1"/>
       <c r="K148" s="1"/>
       <c r="L148" s="1"/>
       <c r="M148" s="1" t="s">
@@ -7872,32 +7879,32 @@
         <v>22</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="P148" s="1"/>
       <c r="Q148" s="1"/>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="C149" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>20</v>
+        <v>460</v>
       </c>
       <c r="F149" s="1">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="H149" s="1">
         <v>0</v>
@@ -7913,38 +7920,38 @@
         <v>22</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="P149" s="1"/>
       <c r="Q149" s="1"/>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="C150" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>119</v>
+        <v>169</v>
       </c>
       <c r="F150" s="1">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>248</v>
+        <v>465</v>
       </c>
       <c r="H150" s="1">
         <v>0</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="J150" s="1">
         <v>0</v>
@@ -7958,48 +7965,40 @@
         <v>22</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="P150" s="1"/>
       <c r="Q150" s="1"/>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C151" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="F151" s="1">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>146</v>
+        <v>470</v>
       </c>
       <c r="H151" s="1">
-        <v>2</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="J151" s="1">
-        <v>0</v>
-      </c>
-      <c r="K151" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="L151" s="1">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I151" s="1"/>
+      <c r="J151" s="1"/>
+      <c r="K151" s="1"/>
+      <c r="L151" s="1"/>
       <c r="M151" s="1" t="s">
         <v>21</v>
       </c>
@@ -8007,38 +8006,38 @@
         <v>22</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="P151" s="1"/>
       <c r="Q151" s="1"/>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C152" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="F152" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>50</v>
+        <v>248</v>
       </c>
       <c r="H152" s="1">
         <v>0</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="J152" s="1">
         <v>0</v>
@@ -8052,20 +8051,20 @@
         <v>22</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="P152" s="1"/>
       <c r="Q152" s="1"/>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C153" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>144</v>
@@ -8074,22 +8073,26 @@
         <v>145</v>
       </c>
       <c r="F153" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>146</v>
       </c>
       <c r="H153" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="J153" s="1">
         <v>0</v>
       </c>
-      <c r="K153" s="1"/>
-      <c r="L153" s="1"/>
+      <c r="K153" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L153" s="1">
+        <v>0</v>
+      </c>
       <c r="M153" s="1" t="s">
         <v>21</v>
       </c>
@@ -8097,17 +8100,17 @@
         <v>22</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="P153" s="1"/>
       <c r="Q153" s="1"/>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C154" s="1">
         <v>2</v>
@@ -8116,19 +8119,19 @@
         <v>19</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="F154" s="1">
         <v>40</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>427</v>
+        <v>50</v>
       </c>
       <c r="H154" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="J154" s="1">
         <v>0</v>
@@ -8142,38 +8145,42 @@
         <v>22</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="P154" s="1"/>
       <c r="Q154" s="1"/>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="C155" s="1">
+        <v>2</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F155" s="1">
         <v>4</v>
       </c>
-      <c r="D155" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="F155" s="1">
-        <v>75</v>
-      </c>
       <c r="G155" s="1" t="s">
-        <v>495</v>
+        <v>146</v>
       </c>
       <c r="H155" s="1">
         <v>0</v>
       </c>
-      <c r="I155" s="1"/>
-      <c r="J155" s="1"/>
+      <c r="I155" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="J155" s="1">
+        <v>0</v>
+      </c>
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
       <c r="M155" s="1" t="s">
@@ -8183,17 +8190,17 @@
         <v>22</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="P155" s="1"/>
       <c r="Q155" s="1"/>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C156" s="1">
         <v>2</v>
@@ -8208,17 +8215,19 @@
         <v>40</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>50</v>
+        <v>427</v>
       </c>
       <c r="H156" s="1">
-        <v>0</v>
-      </c>
-      <c r="K156" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="L156" s="1">
-        <v>0</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="J156" s="1">
+        <v>0</v>
+      </c>
+      <c r="K156" s="1"/>
+      <c r="L156" s="1"/>
       <c r="M156" s="1" t="s">
         <v>21</v>
       </c>
@@ -8226,50 +8235,40 @@
         <v>22</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="P156" s="1" t="s">
-        <v>501</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="P156" s="1"/>
       <c r="Q156" s="1"/>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="C157" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>77</v>
+        <v>494</v>
       </c>
       <c r="F157" s="1">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>119</v>
+        <v>495</v>
       </c>
       <c r="H157" s="1">
-        <v>35</v>
-      </c>
-      <c r="I157" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J157" s="1">
-        <v>0</v>
-      </c>
-      <c r="K157" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="L157" s="1">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I157" s="1"/>
+      <c r="J157" s="1"/>
+      <c r="K157" s="1"/>
+      <c r="L157" s="1"/>
       <c r="M157" s="1" t="s">
         <v>21</v>
       </c>
@@ -8277,20 +8276,20 @@
         <v>22</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="P157" s="1"/>
       <c r="Q157" s="1"/>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="C158" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>19</v>
@@ -8299,22 +8298,16 @@
         <v>119</v>
       </c>
       <c r="F158" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>508</v>
+        <v>50</v>
       </c>
       <c r="H158" s="1">
         <v>0</v>
       </c>
-      <c r="I158" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="J158" s="1">
-        <v>0</v>
-      </c>
       <c r="K158" s="1" t="s">
-        <v>291</v>
+        <v>499</v>
       </c>
       <c r="L158" s="1">
         <v>0</v>
@@ -8326,44 +8319,50 @@
         <v>22</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="P158" s="1"/>
+        <v>500</v>
+      </c>
+      <c r="P158" s="1" t="s">
+        <v>501</v>
+      </c>
       <c r="Q158" s="1"/>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="C159" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E159" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F159" s="1">
         <v>35</v>
       </c>
-      <c r="F159" s="1">
-        <v>40</v>
-      </c>
       <c r="G159" s="1" t="s">
-        <v>512</v>
+        <v>119</v>
       </c>
       <c r="H159" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>513</v>
+        <v>50</v>
       </c>
       <c r="J159" s="1">
-        <v>5</v>
-      </c>
-      <c r="K159" s="1"/>
-      <c r="L159" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="L159" s="1">
+        <v>0</v>
+      </c>
       <c r="M159" s="1" t="s">
         <v>21</v>
       </c>
@@ -8371,20 +8370,20 @@
         <v>22</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="P159" s="1"/>
       <c r="Q159" s="1"/>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C160" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>19</v>
@@ -8393,22 +8392,26 @@
         <v>119</v>
       </c>
       <c r="F160" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="H160" s="1">
         <v>0</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>465</v>
+        <v>248</v>
       </c>
       <c r="J160" s="1">
         <v>0</v>
       </c>
-      <c r="K160" s="1"/>
-      <c r="L160" s="1"/>
+      <c r="K160" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="L160" s="1">
+        <v>0</v>
+      </c>
       <c r="M160" s="1" t="s">
         <v>21</v>
       </c>
@@ -8416,20 +8419,20 @@
         <v>22</v>
       </c>
       <c r="O160" s="1" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="P160" s="1"/>
       <c r="Q160" s="1"/>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="C161" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>19</v>
@@ -8438,19 +8441,19 @@
         <v>35</v>
       </c>
       <c r="F161" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="H161" s="1">
         <v>0</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>465</v>
+        <v>513</v>
       </c>
       <c r="J161" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K161" s="1"/>
       <c r="L161" s="1"/>
@@ -8461,38 +8464,42 @@
         <v>22</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="P161" s="1"/>
       <c r="Q161" s="1"/>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="C162" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>494</v>
+        <v>119</v>
       </c>
       <c r="F162" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="H162" s="1">
         <v>0</v>
       </c>
-      <c r="I162" s="1"/>
-      <c r="J162" s="1"/>
+      <c r="I162" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="J162" s="1">
+        <v>0</v>
+      </c>
       <c r="K162" s="1"/>
       <c r="L162" s="1"/>
       <c r="M162" s="1" t="s">
@@ -8502,17 +8509,17 @@
         <v>22</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1"/>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="C163" s="1">
         <v>3</v>
@@ -8524,26 +8531,22 @@
         <v>35</v>
       </c>
       <c r="F163" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>50</v>
+        <v>521</v>
       </c>
       <c r="H163" s="1">
         <v>0</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>532</v>
+        <v>465</v>
       </c>
       <c r="J163" s="1">
         <v>0</v>
       </c>
-      <c r="K163" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="L163" s="1">
-        <v>0</v>
-      </c>
+      <c r="K163" s="1"/>
+      <c r="L163" s="1"/>
       <c r="M163" s="1" t="s">
         <v>21</v>
       </c>
@@ -8551,17 +8554,17 @@
         <v>22</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="P163" s="1"/>
       <c r="Q163" s="1"/>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="C164" s="1">
         <v>3</v>
@@ -8570,30 +8573,120 @@
         <v>19</v>
       </c>
       <c r="E164" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="F164" s="1">
+        <v>80</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="H164" s="1">
+        <v>0</v>
+      </c>
+      <c r="I164" s="1"/>
+      <c r="J164" s="1"/>
+      <c r="K164" s="1"/>
+      <c r="L164" s="1"/>
+      <c r="M164" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N164" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O164" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="P164" s="1"/>
+      <c r="Q164" s="1"/>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C165" s="1">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F165" s="1">
+        <v>60</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H165" s="1">
+        <v>0</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="J165" s="1">
+        <v>0</v>
+      </c>
+      <c r="K165" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L165" s="1">
+        <v>0</v>
+      </c>
+      <c r="M165" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N165" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O165" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="P165" s="1"/>
+      <c r="Q165" s="1"/>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C166" s="1">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F164" s="1">
+      <c r="F166" s="1">
         <v>50</v>
       </c>
-      <c r="G164" s="1" t="s">
+      <c r="G166" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H164" s="1">
-        <v>0</v>
-      </c>
-      <c r="I164" s="1" t="s">
+      <c r="H166" s="1">
+        <v>0</v>
+      </c>
+      <c r="I166" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="J164" s="1">
-        <v>0</v>
-      </c>
-      <c r="M164" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N164" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O164" s="1" t="s">
+      <c r="J166" s="1">
+        <v>0</v>
+      </c>
+      <c r="M166" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N166" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O166" s="1" t="s">
         <v>537</v>
       </c>
     </row>
